--- a/shop-main/Dalaila Botique/dalaila satement/copy.xlsx
+++ b/shop-main/Dalaila Botique/dalaila satement/copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\shop-main\Dalaila Botique\dalaila satement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0DEB16-58F6-4E08-9704-FB32ACF11F83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AEF46A-D680-43DE-8714-3E18D66674B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5640" xr2:uid="{AFF0AB6C-1450-46AA-A0E4-B4A4A7173A68}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Dalaila</t>
   </si>
@@ -108,19 +108,46 @@
     <t>july,2022</t>
   </si>
   <si>
-    <t>REMAINING</t>
-  </si>
-  <si>
     <t>September,2022</t>
   </si>
   <si>
     <t>October,2022</t>
   </si>
   <si>
-    <t>November,202</t>
-  </si>
-  <si>
     <t>August,2022</t>
+  </si>
+  <si>
+    <t>November,2022</t>
+  </si>
+  <si>
+    <t>December,2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January,2023 </t>
+  </si>
+  <si>
+    <t>February,2023</t>
+  </si>
+  <si>
+    <t>March,2023</t>
+  </si>
+  <si>
+    <t>April,2023</t>
+  </si>
+  <si>
+    <t>May,2023</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>##2034749491</t>
+  </si>
+  <si>
+    <t>##3023530677</t>
   </si>
 </sst>
 </file>
@@ -156,7 +183,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -190,11 +217,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -203,9 +243,13 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,23 +564,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91583C42-68ED-44DA-9782-EC3336F370E4}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -548,7 +594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -558,7 +604,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -568,7 +614,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -579,7 +625,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -590,7 +636,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -599,12 +645,8 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="F8">
-        <f>SUM(B4:B25)+B26+B27</f>
-        <v>703175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -613,12 +655,10 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="G9">
-        <f>SUM(D4:D26)</f>
-        <v>431961</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -627,8 +667,10 @@
       <c r="D10" s="2">
         <v>50000</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -637,8 +679,10 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -649,12 +693,10 @@
       <c r="D12" s="2">
         <v>50000</v>
       </c>
-      <c r="G12">
-        <f>F8-G9</f>
-        <v>271214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -663,8 +705,10 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -673,8 +717,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
@@ -683,8 +729,10 @@
       <c r="D15" s="2">
         <v>81961</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
@@ -693,8 +741,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -703,8 +753,10 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
@@ -713,8 +765,10 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
@@ -723,8 +777,10 @@
       <c r="D19" s="2">
         <v>100000</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -733,8 +789,10 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
@@ -743,8 +801,10 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -753,8 +813,10 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
@@ -763,8 +825,10 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -773,8 +837,10 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -783,8 +849,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -795,10 +863,12 @@
       <c r="D26" s="2">
         <v>150000</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2">
         <v>54506</v>
@@ -807,20 +877,27 @@
       <c r="D27" s="2">
         <v>150000</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27">
+        <v>2032903793</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>71131</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>148666</v>
@@ -829,52 +906,165 @@
       <c r="D29" s="2">
         <v>100000</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>2033582656</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>36947</v>
+        <v>120379</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <v>100000</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="2"/>
+      <c r="E30">
+        <v>2034560525</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2">
+        <v>77266</v>
+      </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
+      <c r="D31" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="7">
+        <v>44915</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="B32" s="2">
-        <f>SUM(B4:B31)</f>
-        <v>959919</v>
+        <v>46779</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
-        <f>SUM(D4:D31)</f>
-        <v>781961</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+        <v>50000</v>
+      </c>
+      <c r="E32">
+        <v>2034749520</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="9"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2">
+        <v>43628</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2">
-        <f>B32-D32</f>
-        <v>177958</v>
+        <v>70629</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="D34" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="7">
+        <v>45012</v>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2">
+        <v>84953</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46545</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <v>80592</v>
+      </c>
+      <c r="E36">
+        <v>20847</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <f>SUM(B4:B36)</f>
+        <v>1413151</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2">
+        <f>SUM(D4:D37)</f>
+        <v>1112553</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2">
+        <f>B38-D38</f>
+        <v>300598</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
